--- a/data/trans_orig/P15D$nada-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15D$nada-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15455</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>44995</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31376</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42751</t>
+          <t>43144</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59768</t>
+          <t>60051</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>39821</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45580</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68540</t>
+          <t>67622</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51379</t>
+          <t>50824</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70627</t>
+          <t>69211</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>101610</t>
+          <t>102408</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>132462</t>
+          <t>132182</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,25%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25876</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26286</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>40731</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41466</t>
+          <t>40312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27379</t>
+          <t>26563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42438</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>49562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>38813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50389</t>
+          <t>51566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45687</t>
+          <t>45399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64903</t>
+          <t>64859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>22598</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72193</t>
+          <t>72178</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95363</t>
+          <t>96554</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>15379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61732</t>
+          <t>61680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22560</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6407,19 +6407,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50399</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>954</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36653</t>
+          <t>35547</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54834</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>49852</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72637</t>
+          <t>71573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56722</t>
+          <t>56671</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87176</t>
+          <t>86248</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>87992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>122858</t>
+          <t>123051</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>162758</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>31828</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60169</t>
+          <t>60281</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>149176</t>
+          <t>146400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>181649</t>
+          <t>181897</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>123411</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>158211</t>
+          <t>153519</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>284961</t>
+          <t>281031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>331171</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35781</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>58572</t>
+          <t>57975</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -7924,12 +7924,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>20942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -8836,12 +8836,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33421</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>29702</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74370</t>
+          <t>73522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -9292,12 +9292,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9362,12 +9362,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16935</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>29541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>37522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54716</t>
+          <t>55536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -9748,12 +9748,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9833,19 +9833,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -10013,47 +10013,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>11488</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>11812</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>32033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47456</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50232</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68923</t>
+          <t>68648</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>44783</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46519</t>
+          <t>45605</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74381</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36131</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>29343</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33563</t>
+          <t>33532</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>59360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>107727</t>
+          <t>106898</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135418</t>
+          <t>135360</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109543</t>
+          <t>109229</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>136949</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>226554</t>
+          <t>224871</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>266569</t>
+          <t>263315</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -10660,12 +10660,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32869</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10675,12 +10675,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>57173</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>35684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -11345,32 +11345,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -11801,32 +11801,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11836,32 +11836,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>26983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>22657</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>18773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>31979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -12257,32 +12257,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12292,32 +12292,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>413</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12327,32 +12327,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20584</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>31733</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41714</t>
+          <t>51039</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25230</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>42120</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>78690</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54465</t>
+          <t>65295</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75242</t>
+          <t>89703</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -12713,32 +12713,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12748,32 +12748,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12783,32 +12783,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>24753</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30517</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>54065</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41318</t>
+          <t>44170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>63605</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -13169,32 +13169,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13204,32 +13204,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16370</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13239,39 +13239,39 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>711</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -13512,27 +13512,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>41026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13660,32 +13660,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13695,32 +13695,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>33202</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46886</t>
+          <t>45045</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29843</t>
+          <t>30512</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>49144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>72598</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56347</t>
+          <t>58870</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87247</t>
+          <t>88364</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50287</t>
+          <t>53367</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71282</t>
+          <t>74691</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>115708</t>
+          <t>130144</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100082</t>
+          <t>113387</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>130010</t>
+          <t>145645</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>105799</t>
+          <t>117502</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>94072</t>
+          <t>103923</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>117895</t>
+          <t>130872</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>221507</t>
+          <t>247645</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>199371</t>
+          <t>225810</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>240878</t>
+          <t>268820</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -14081,32 +14081,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>50878</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14116,32 +14116,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>26260</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>39472</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14151,32 +14151,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>55915</t>
+          <t>62260</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>44194</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>71470</t>
+          <t>81241</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
